--- a/assetcore/public/import_templates/01c_vi_tri.xlsx
+++ b/assetcore/public/import_templates/01c_vi_tri.xlsx
@@ -536,8 +536,8 @@
     <col width="26" customWidth="1" min="4" max="4"/>
     <col width="30" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="25" customWidth="1" min="7" max="7"/>
-    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
@@ -581,12 +581,12 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>emergency_contact</t>
+          <t>dept_head</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>dept_head</t>
+          <t>contact_phone</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
@@ -628,12 +628,12 @@
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>Liên hệ khẩn cấp</t>
+          <t>Người phụ trách (email)</t>
         </is>
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
-          <t>Trưởng khu vực (email)</t>
+          <t>Số liên hệ</t>
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr">
@@ -675,12 +675,12 @@
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>Số DT hoặc email liên hệ khẩn cấp.</t>
+          <t>Email User phụ trách vị trí.</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>Email User phụ trách vị trí.</t>
+          <t>Số liên hệ. Khi để trống, hệ thống sẽ tự lấy theo số di động của người phụ trách (mobile_no).</t>
         </is>
       </c>
       <c r="I4" s="6" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
+          <t>nguyen.van.a@hospital.vn</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
           <t>0901234567</t>
-        </is>
-      </c>
-      <c r="H5" s="7" t="inlineStr">
-        <is>
-          <t>nguyen.van.a@hospital.vn</t>
         </is>
       </c>
       <c r="I5" s="7" t="inlineStr">

--- a/assetcore/public/import_templates/01c_vi_tri.xlsx
+++ b/assetcore/public/import_templates/01c_vi_tri.xlsx
@@ -544,7 +544,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📋 HƯỚNG DẪN IMPORT: Vị trí (Location)  |  Điền dữ liệu từ hàng 5 trở xuống. Cột đỏ = bắt buộc. Không xóa hàng 2-4.</t>
+          <t>📋 HƯỚNG DẪN IMPORT: Vị trí (Location)  |  Điền dữ liệu từ HÀNG 6 trở xuống (hàng 5 là ví dụ mẫu, hệ thống bỏ qua). Cột đỏ = bắt buộc. Không xoá/không sửa hàng 1-5. Cột tham chiếu (danh mục, khoa phòng, vị trí, model, nhà cung cấp) điền TÊN, không điền mã.</t>
         </is>
       </c>
     </row>
@@ -655,17 +655,17 @@
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Tên vị trí cha (phải tồn tại). VD: Tòa nhà A.</t>
+          <t>Tên vị trí cấp trên. Điền TÊN, KHÔNG điền mã hệ thống. VD: Tòa nhà A. Phải tồn tại hoặc được khai ở hàng phía trên.</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>ICU / OR / Lab / Imaging / General Ward / Storage / Office</t>
+          <t>Hồi sức tích cực / Phòng mổ / Xét nghiệm / Chẩn đoán hình ảnh / Khoa lâm sàng thường / Kho / Văn phòng.</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Standard / Enhanced / Isolation</t>
+          <t>Tiêu chuẩn / Tăng cường / Cách ly.</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>Email User phụ trách vị trí.</t>
+          <t>Email người phụ trách vị trí. Sai email thì dòng vẫn nhập được nhưng để trống ô này.</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>ICU</t>
+          <t>Hồi sức tích cực</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>Tiêu chuẩn</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
@@ -1841,16 +1841,16 @@
     <mergeCell ref="A1:I1"/>
   </mergeCells>
   <dataValidations count="4">
-    <dataValidation sqref="D5:D105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
-      <formula1>"ICU,OR,Lab,Imaging,General Ward,Storage,Office"</formula1>
+    <dataValidation sqref="D6:D105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
+      <formula1>"Hồi sức tích cực,Phòng mổ,Xét nghiệm,Chẩn đoán hình ảnh,Khoa lâm sàng thường,Kho,Văn phòng"</formula1>
     </dataValidation>
-    <dataValidation sqref="E5:E105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
-      <formula1>"Standard,Enhanced,Isolation"</formula1>
+    <dataValidation sqref="E6:E105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
+      <formula1>"Tiêu chuẩn,Tăng cường,Cách ly"</formula1>
     </dataValidation>
-    <dataValidation sqref="F5:F105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
+    <dataValidation sqref="F6:F105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
       <formula1>"1,0"</formula1>
     </dataValidation>
-    <dataValidation sqref="I5:I105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
+    <dataValidation sqref="I6:I105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
       <formula1>"1,0"</formula1>
     </dataValidation>
   </dataValidations>

--- a/assetcore/public/import_templates/01c_vi_tri.xlsx
+++ b/assetcore/public/import_templates/01c_vi_tri.xlsx
@@ -1841,16 +1841,16 @@
     <mergeCell ref="A1:I1"/>
   </mergeCells>
   <dataValidations count="4">
-    <dataValidation sqref="D6:D105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
+    <dataValidation sqref="D6:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
       <formula1>"Hồi sức tích cực,Phòng mổ,Xét nghiệm,Chẩn đoán hình ảnh,Khoa lâm sàng thường,Kho,Văn phòng"</formula1>
     </dataValidation>
-    <dataValidation sqref="E6:E105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
+    <dataValidation sqref="E6:E1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
       <formula1>"Tiêu chuẩn,Tăng cường,Cách ly"</formula1>
     </dataValidation>
-    <dataValidation sqref="F6:F105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
+    <dataValidation sqref="F6:F1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
       <formula1>"1,0"</formula1>
     </dataValidation>
-    <dataValidation sqref="I6:I105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
+    <dataValidation sqref="I6:I1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
       <formula1>"1,0"</formula1>
     </dataValidation>
   </dataValidations>
